--- a/NORM.xlsx
+++ b/NORM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E221B0-491C-4061-A9C5-68C4496B8DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28689FD-17DE-4495-8C3C-99623324A534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Norm Kadro Şablonu" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -473,16 +476,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -499,7 +502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -517,7 +520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -535,7 +538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -553,7 +556,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -564,14 +567,14 @@
         <v>23</v>
       </c>
       <c r="D5" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -589,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -607,7 +610,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -625,7 +628,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -643,7 +646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -661,7 +664,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>

--- a/NORM.xlsx
+++ b/NORM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28689FD-17DE-4495-8C3C-99623324A534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752E7167-5637-411B-AD2D-2A90C94B3D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Norm Kadro Şablonu" sheetId="1" r:id="rId1"/>
@@ -476,16 +476,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.25" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -502,7 +502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -556,7 +556,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -567,14 +567,14 @@
         <v>23</v>
       </c>
       <c r="D5" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -610,7 +610,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -628,7 +628,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -646,7 +646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -664,7 +664,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>

--- a/NORM.xlsx
+++ b/NORM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752E7167-5637-411B-AD2D-2A90C94B3D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B635D3E3-B562-40DB-BDC8-C22C75F489C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -567,11 +567,11 @@
         <v>23</v>
       </c>
       <c r="D5" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
